--- a/data/reference/merchants.xlsx
+++ b/data/reference/merchants.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GTCo Plaza Retail Ltd</t>
+          <t>Ikeja Pharmacy Stores</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Pharmacy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2022-03-14</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -496,27 +496,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wuse Market Traders Union</t>
+          <t>Ajeromi-Ifelodun Groceries Mart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Groceries</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abuja</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Municipal Area Council</t>
+          <t>Ajeromi-Ifelodun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2023-07-22</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -526,32 +526,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MRC0003</t>
+          <t>MRC0004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sabon Gari Electronics Ltd</t>
+          <t>Alimosho Fashion Mart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Fashion</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kano</t>
+          <t>Lagos</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kano Municipal</t>
+          <t>Alimosho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -561,32 +561,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MRC0004</t>
+          <t>MRC0005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GRA Supermarket Ltd</t>
+          <t>Kuje Fashion Plaza</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Supermarket</t>
+          <t>Fashion</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rivers</t>
+          <t>Abuja</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Port Harcourt</t>
+          <t>Kuje</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -596,12 +596,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MRC0005</t>
+          <t>MRC0006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bodija Fuel Station Ltd</t>
+          <t>Alimosho Fuel Station Enterprises</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -611,20 +611,6390 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MRC0007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Port Harcourt Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MRC0008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Eleme Pharmacy Ventures</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MRC0009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ibadan North Fuel Station Ltd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Oyo</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Ibadan North</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2019-09-08</t>
-        </is>
-      </c>
-      <c r="G6" t="b">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2022-10-29</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MRC0010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Services Stores</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MRC0011</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gwagwalada Groceries Ventures</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MRC0012</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fagge Supermarket Concepts</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2023-11-16</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MRC0013</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Port Harcourt Pharmacy Concepts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MRC0014</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Egbeda Electronics Mart</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MRC0015</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fagge Hospitality Stores</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2022-01-30</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MRC0016</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alimosho Retail Ventures</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MRC0017</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alimosho Services Concepts</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MRC0018</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fagge Supermarket Stores</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MRC0019</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Egbeda Pharmacy Concepts</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MRC0020</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Restaurant Stores</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MRC0021</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ikeja Groceries Stores</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MRC0022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nassarawa Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MRC0024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nassarawa Pharmacy Mart</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MRC0025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun Pharmacy Ventures</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2022-04-30</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MRC0026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Electronics Plaza</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MRC0027</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Eleme Electronics Mart</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MRC0028</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Eleme Hospitality Mart</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MRC0029</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Municipal Area Council Services Enterprises</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Municipal Area Council</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2023-03-08</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MRC0030</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Fashion Ltd</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MRC0032</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ikeja Supermarket Ventures</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MRC0033</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ibadan North Electronics Concepts</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MRC0034</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gwagwalada Hospitality Ventures</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MRC0035</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bwari Pharmacy Plaza</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bwari</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2022-02-26</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MRC0036</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nassarawa Supermarket Ltd</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MRC0037</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Port Harcourt Services Mart</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MRC0038</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ikeja Retail Stores</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MRC0039</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Port Harcourt Hospitality Stores</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MRC0040</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bwari Services Mart</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bwari</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2023-04-09</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MRC0041</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fagge Fashion Ltd</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MRC0043</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Fuel Station Plaza</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MRC0044</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ikeja Fuel Station Concepts</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MRC0045</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alimosho Fashion Stores</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MRC0046</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kano Municipal Pharmacy Plaza</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MRC0047</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Surulere Hospitality Ltd</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Surulere</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MRC0049</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ibadan North Groceries Ventures</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MRC0050</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Fagge Fashion Ventures</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MRC0051</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kuje Retail Plaza</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MRC0052</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fagge Fuel Station Concepts</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MRC0053</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kano Municipal Fashion Enterprises</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MRC0054</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Egbeda Hospitality Ltd</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MRC0055</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Hospitality Ventures</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2022-12-11</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MRC0056</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ibadan North Electronics Ltd</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MRC0057</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kuje Groceries Mart</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MRC0058</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2022-03-27</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MRC0059</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Pharmacy Stores</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2022-03-02</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MRC0060</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gwagwalada Fuel Station Stores</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2022-02-26</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MRC0061</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Fagge Groceries Ltd</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MRC0062</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ibadan North Groceries Mart</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2024-09-22</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MRC0063</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gwagwalada Groceries Stores</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MRC0064</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Nassarawa Pharmacy Mart</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MRC0065</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Groceries Stores</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MRC0066</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun Electronics Enterprises</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MRC0067</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Port Harcourt Pharmacy Mart</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2023-03-08</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MRC0068</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ikeja Fuel Station Ventures</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MRC0069</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Port Harcourt Pharmacy Stores</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MRC0070</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Nassarawa Retail Ltd</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MRC0071</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Municipal Area Council Restaurant Mart</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Municipal Area Council</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MRC0072</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Municipal Area Council Pharmacy Enterprises</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Municipal Area Council</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MRC0073</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Bwari Groceries Enterprises</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Bwari</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MRC0074</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Nassarawa Electronics Stores</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MRC0075</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kuje Retail Stores</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MRC0076</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nassarawa Fashion Enterprises</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MRC0077</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Surulere Retail Ventures</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Surulere</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MRC0078</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Fagge Pharmacy Ventures</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MRC0079</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kuje Restaurant Enterprises</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MRC0080</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Hospitality Plaza</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MRC0081</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Retail Ltd</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MRC0082</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Port Harcourt Groceries Mart</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MRC0083</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Services Mart</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MRC0084</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ibadan North Pharmacy Ltd</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MRC0085</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Egbeda Fashion Enterprises</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MRC0086</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Eleme Restaurant Concepts</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MRC0087</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Eleme Pharmacy Concepts</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MRC0088</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Eleme Electronics Stores</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MRC0089</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nassarawa Electronics Mart</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MRC0090</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ibadan North Pharmacy Enterprises</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MRC0091</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Egbeda Restaurant Plaza</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MRC0092</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kuje Electronics Concepts</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MRC0093</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Groceries Ventures</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MRC0094</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Bwari Electronics Ltd</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Bwari</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MRC0095</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nassarawa Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MRC0096</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ibadan North Fuel Station Plaza</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MRC0097</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ikeja Fuel Station Stores</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MRC0098</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Retail Mart</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MRC0099</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Surulere Electronics Ventures</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Surulere</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MRC0100</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Egbeda Restaurant Ventures</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MRC0103</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Hospitality Plaza</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MRC0104</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fagge Pharmacy Ventures</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MRC0105</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Eleme Supermarket Concepts</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MRC0106</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Eti-Osa Fashion Enterprises</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Eti-Osa</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MRC0107</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ibadan North Electronics Stores</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MRC0108</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Bwari Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Bwari</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MRC0109</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Fagge Retail Stores</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2023-07-26</t>
+        </is>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MRC0110</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Egbeda Retail Ventures</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MRC0111</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Eti-Osa Pharmacy Ventures</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Eti-Osa</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="G105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MRC0112</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Nassarawa Hospitality Ventures</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2022-07-16</t>
+        </is>
+      </c>
+      <c r="G106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MRC0113</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Kano Municipal Pharmacy Plaza</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2023-03-14</t>
+        </is>
+      </c>
+      <c r="G107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MRC0114</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Eleme Fuel Station Concepts</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="G108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MRC0115</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Municipal Area Council Fuel Station Mart</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Municipal Area Council</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="G109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MRC0116</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Surulere Electronics Ventures</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Surulere</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="G110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MRC0117</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Restaurant Stores</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="G111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MRC0118</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Fagge Fuel Station Enterprises</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="G112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MRC0119</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ibadan North Restaurant Stores</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2022-04-11</t>
+        </is>
+      </c>
+      <c r="G113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MRC0120</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ikeja Fashion Stores</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="G114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MRC0121</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Bwari Supermarket Concepts</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Bwari</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="G115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MRC0122</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Kuje Pharmacy Ventures</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="G116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MRC0124</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Egbeda Groceries Ventures</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="G117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MRC0125</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun Retail Enterprises</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="G118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MRC0126</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Fagge Fashion Ltd</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="G119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MRC0127</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Municipal Area Council Pharmacy Ventures</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Municipal Area Council</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+      <c r="G120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MRC0128</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun Retail Enterprises</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2022-12-07</t>
+        </is>
+      </c>
+      <c r="G121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MRC0129</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Port Harcourt Hospitality Concepts</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="G122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MRC0130</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Fagge Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="G123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MRC0131</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Nassarawa Electronics Plaza</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="G124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MRC0132</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Eleme Hospitality Ventures</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2023-03-18</t>
+        </is>
+      </c>
+      <c r="G125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MRC0133</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Restaurant Ventures</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="G126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MRC0134</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Eti-Osa Supermarket Stores</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Eti-Osa</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="G127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MRC0135</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Fagge Retail Plaza</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MRC0136</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Gwagwalada Pharmacy Enterprises</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MRC0137</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Eleme Retail Mart</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MRC0138</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Fagge Hospitality Ventures</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MRC0140</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Fagge Retail Ltd</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="G132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MRC0141</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Gwagwalada Services Enterprises</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="G133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MRC0142</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Hospitality Enterprises</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2023-12-13</t>
+        </is>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MRC0143</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Obio-Akpor Pharmacy Stores</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Obio-Akpor</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="G135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MRC0144</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Port Harcourt Hospitality Ventures</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2022-01-19</t>
+        </is>
+      </c>
+      <c r="G136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MRC0145</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Kuje Pharmacy Concepts</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="G137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MRC0146</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Egbeda Pharmacy Ltd</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="G138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MRC0147</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Port Harcourt Pharmacy Ltd</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="G139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MRC0148</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ikeja Hospitality Enterprises</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Ikeja</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="G140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MRC0150</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Kano Municipal Retail Mart</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="G141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MRC0152</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Fagge Electronics Ltd</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="G142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MRC0153</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Kano Municipal Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="G143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MRC0154</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Alimosho Electronics Ventures</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="G144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MRC0155</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Alimosho Groceries Mart</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="G145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MRC0156</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ibadan North Hospitality Plaza</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="G146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MRC0157</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Eleme Fuel Station Enterprises</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2022-09-25</t>
+        </is>
+      </c>
+      <c r="G147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>MRC0158</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Egbeda Groceries Ventures</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="G148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MRC0159</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Eleme Groceries Stores</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="G149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MRC0161</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Alimosho Retail Plaza</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="G150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MRC0162</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Fagge Retail Stores</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="G151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MRC0163</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kano Municipal Fashion Enterprises</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="G152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MRC0164</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Kuje Groceries Mart</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Kuje</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="G153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>MRC0165</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Port Harcourt Groceries Ltd</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="G154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MRC0166</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Egbeda Services Enterprises</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="G155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MRC0167</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Eleme Fuel Station Enterprises</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2023-02-12</t>
+        </is>
+      </c>
+      <c r="G156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MRC0168</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Kano Municipal Services Ltd</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2023-07-02</t>
+        </is>
+      </c>
+      <c r="G157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MRC0169</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Retail Ltd</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="G158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MRC0170</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Egbeda Retail Ventures</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="G159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MRC0171</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Ibadan North Electronics Plaza</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Ibadan North</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="G160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MRC0172</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Port Harcourt Services Plaza</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2022-05-12</t>
+        </is>
+      </c>
+      <c r="G161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MRC0173</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Surulere Restaurant Plaza</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Surulere</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="G162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MRC0174</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Alimosho Restaurant Plaza</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Alimosho</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2022-01-12</t>
+        </is>
+      </c>
+      <c r="G163" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MRC0175</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Nassarawa Retail Plaza</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="G164" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MRC0176</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Port Harcourt Fuel Station Ventures</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Fuel Station</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="G165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>MRC0177</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun Supermarket Plaza</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Ajeromi-Ifelodun</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="G166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>MRC0178</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Eleme Supermarket Concepts</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Eleme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2023-06-11</t>
+        </is>
+      </c>
+      <c r="G167" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MRC0179</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Gwagwalada Hospitality Stores</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="G168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MRC0180</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Kano Municipal Retail Concepts</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="G169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MRC0181</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Gwagwalada Hospitality Ltd</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Gwagwalada</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="G170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>MRC0182</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Municipal Area Council Supermarket Ltd</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Municipal Area Council</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="G171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>MRC0183</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Nassarawa Pharmacy Mart</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="G172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MRC0184</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Fagge Fashion Plaza</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="G173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MRC0185</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Bwari Groceries Enterprises</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Bwari</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="G174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MRC0186</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Retail Enterprises</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="G175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MRC0187</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Egbeda Supermarket Ventures</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Egbeda</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="G176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>MRC0188</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Fagge Restaurant Mart</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="G177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>MRC0189</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Port Harcourt Fashion Mart</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="G178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>MRC0190</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Kano Municipal Restaurant Concepts</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2023-04-09</t>
+        </is>
+      </c>
+      <c r="G179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>MRC0191</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Fagge Electronics Plaza</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Fagge</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="G180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MRC0192</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ibadan South-West Groceries Ventures</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Oyo</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Ibadan South-West</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="G181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>MRC0193</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Kano Municipal Electronics Plaza</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Kano Municipal</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2022-04-02</t>
+        </is>
+      </c>
+      <c r="G182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>MRC0194</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Surulere Pharmacy Enterprises</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Surulere</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="G183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>MRC0195</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Eti-Osa Hospitality Plaza</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Eti-Osa</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="G184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>MRC0196</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Nassarawa Retail Mart</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Nassarawa</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="G185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>MRC0197</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Port Harcourt Groceries Plaza</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Rivers</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="G186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MRC0199</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Surulere Electronics Concepts</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Surulere</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="G187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>MRC0200</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Eti-Osa Retail Enterprises</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Eti-Osa</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="G188" t="b">
         <v>0</v>
       </c>
     </row>
